--- a/DEVELOPMENT_ALL_OLD_NEW/H&M/HM.0657 - C-2+ BERAVLY LIGHT.xlsx
+++ b/DEVELOPMENT_ALL_OLD_NEW/H&M/HM.0657 - C-2+ BERAVLY LIGHT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\TC.DEVELOPMENT.BRAND FILE 2\H&amp;M\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FBA4637-F53B-4854-9BC0-239C364A87A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BDF783B-844D-4496-8CC7-93A6EE9EAA08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1871,29 +1871,47 @@
     <xf numFmtId="0" fontId="39" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="41" fillId="5" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="41" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="41" fillId="5" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="58" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="5" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="45" fillId="5" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="41" fillId="10" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="41" fillId="10" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="41" fillId="10" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="58" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1901,29 +1919,14 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="6" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="9" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1931,93 +1934,93 @@
     <xf numFmtId="0" fontId="39" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="58" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="3" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="3" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="3" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="39" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="46" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="41" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="42" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="37" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="23" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="26" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2027,18 +2030,30 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="29" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="14" fontId="9" fillId="4" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="4" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="4" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
@@ -2048,18 +2063,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="4" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="4" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="4" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -2075,145 +2078,142 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="23" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="39" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="26" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="46" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="41" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="8" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="6" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="42" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="8" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="37" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="3" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="3" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="3" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="41" fillId="5" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="41" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="41" fillId="5" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="45" fillId="5" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="41" fillId="10" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="41" fillId="10" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="41" fillId="10" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="5" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3634,21 +3634,21 @@
       <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="194">
+      <c r="C2" s="159">
         <v>46266</v>
       </c>
-      <c r="D2" s="195"/>
-      <c r="E2" s="196"/>
-      <c r="F2" s="194" t="s">
+      <c r="D2" s="160"/>
+      <c r="E2" s="161"/>
+      <c r="F2" s="159" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="195"/>
-      <c r="H2" s="197" t="s">
+      <c r="G2" s="160"/>
+      <c r="H2" s="162" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="198"/>
-      <c r="J2" s="198"/>
-      <c r="K2" s="199"/>
+      <c r="I2" s="163"/>
+      <c r="J2" s="163"/>
+      <c r="K2" s="164"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
     </row>
@@ -3657,17 +3657,17 @@
       <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="194" t="s">
+      <c r="C3" s="159" t="s">
         <v>90</v>
       </c>
-      <c r="D3" s="195"/>
-      <c r="E3" s="196"/>
-      <c r="F3" s="200"/>
-      <c r="G3" s="201"/>
-      <c r="H3" s="206" t="s">
+      <c r="D3" s="160"/>
+      <c r="E3" s="161"/>
+      <c r="F3" s="165"/>
+      <c r="G3" s="166"/>
+      <c r="H3" s="171" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="207"/>
+      <c r="I3" s="172"/>
       <c r="J3" s="7"/>
       <c r="K3" s="8"/>
       <c r="L3" s="4"/>
@@ -3681,17 +3681,17 @@
       <c r="B4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="208" t="s">
+      <c r="C4" s="173" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="209"/>
-      <c r="E4" s="210"/>
-      <c r="F4" s="202"/>
-      <c r="G4" s="203"/>
-      <c r="H4" s="211"/>
-      <c r="I4" s="212"/>
-      <c r="J4" s="211"/>
-      <c r="K4" s="212"/>
+      <c r="D4" s="174"/>
+      <c r="E4" s="175"/>
+      <c r="F4" s="167"/>
+      <c r="G4" s="168"/>
+      <c r="H4" s="176"/>
+      <c r="I4" s="177"/>
+      <c r="J4" s="176"/>
+      <c r="K4" s="177"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
     </row>
@@ -3700,17 +3700,17 @@
       <c r="B5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="213">
+      <c r="C5" s="178">
         <v>512241880</v>
       </c>
-      <c r="D5" s="214"/>
-      <c r="E5" s="215"/>
-      <c r="F5" s="202"/>
-      <c r="G5" s="203"/>
-      <c r="H5" s="180"/>
-      <c r="I5" s="181"/>
-      <c r="J5" s="180"/>
-      <c r="K5" s="181"/>
+      <c r="D5" s="179"/>
+      <c r="E5" s="180"/>
+      <c r="F5" s="167"/>
+      <c r="G5" s="168"/>
+      <c r="H5" s="181"/>
+      <c r="I5" s="182"/>
+      <c r="J5" s="181"/>
+      <c r="K5" s="182"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
     </row>
@@ -3719,17 +3719,17 @@
       <c r="B6" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="216" t="s">
+      <c r="C6" s="183" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="217"/>
-      <c r="E6" s="218"/>
-      <c r="F6" s="202"/>
-      <c r="G6" s="203"/>
-      <c r="H6" s="180"/>
-      <c r="I6" s="181"/>
-      <c r="J6" s="180"/>
-      <c r="K6" s="181"/>
+      <c r="D6" s="184"/>
+      <c r="E6" s="185"/>
+      <c r="F6" s="167"/>
+      <c r="G6" s="168"/>
+      <c r="H6" s="181"/>
+      <c r="I6" s="182"/>
+      <c r="J6" s="181"/>
+      <c r="K6" s="182"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
     </row>
@@ -3738,17 +3738,17 @@
       <c r="B7" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="191" t="s">
+      <c r="C7" s="192" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="192"/>
-      <c r="E7" s="193"/>
-      <c r="F7" s="202"/>
-      <c r="G7" s="203"/>
-      <c r="H7" s="180"/>
-      <c r="I7" s="181"/>
-      <c r="J7" s="180"/>
-      <c r="K7" s="181"/>
+      <c r="D7" s="193"/>
+      <c r="E7" s="194"/>
+      <c r="F7" s="167"/>
+      <c r="G7" s="168"/>
+      <c r="H7" s="181"/>
+      <c r="I7" s="182"/>
+      <c r="J7" s="181"/>
+      <c r="K7" s="182"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
     </row>
@@ -3757,15 +3757,15 @@
       <c r="B8" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="188"/>
-      <c r="D8" s="189"/>
-      <c r="E8" s="190"/>
-      <c r="F8" s="202"/>
-      <c r="G8" s="203"/>
+      <c r="C8" s="186"/>
+      <c r="D8" s="187"/>
+      <c r="E8" s="188"/>
+      <c r="F8" s="167"/>
+      <c r="G8" s="168"/>
       <c r="H8" s="11"/>
       <c r="I8" s="12"/>
-      <c r="J8" s="180"/>
-      <c r="K8" s="181"/>
+      <c r="J8" s="181"/>
+      <c r="K8" s="182"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
     </row>
@@ -3774,17 +3774,17 @@
       <c r="B9" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="185">
+      <c r="C9" s="189">
         <v>5</v>
       </c>
-      <c r="D9" s="186"/>
-      <c r="E9" s="187"/>
-      <c r="F9" s="202"/>
-      <c r="G9" s="203"/>
+      <c r="D9" s="190"/>
+      <c r="E9" s="191"/>
+      <c r="F9" s="167"/>
+      <c r="G9" s="168"/>
       <c r="H9" s="11"/>
       <c r="I9" s="12"/>
-      <c r="J9" s="180"/>
-      <c r="K9" s="181"/>
+      <c r="J9" s="181"/>
+      <c r="K9" s="182"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
     </row>
@@ -3793,15 +3793,15 @@
       <c r="B10" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="185"/>
-      <c r="D10" s="186"/>
-      <c r="E10" s="187"/>
-      <c r="F10" s="202"/>
-      <c r="G10" s="203"/>
+      <c r="C10" s="189"/>
+      <c r="D10" s="190"/>
+      <c r="E10" s="191"/>
+      <c r="F10" s="167"/>
+      <c r="G10" s="168"/>
       <c r="H10" s="11"/>
       <c r="I10" s="12"/>
-      <c r="J10" s="180"/>
-      <c r="K10" s="181"/>
+      <c r="J10" s="181"/>
+      <c r="K10" s="182"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
     </row>
@@ -3810,15 +3810,15 @@
       <c r="B11" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="182"/>
-      <c r="D11" s="183"/>
-      <c r="E11" s="184"/>
-      <c r="F11" s="202"/>
-      <c r="G11" s="203"/>
-      <c r="H11" s="180"/>
-      <c r="I11" s="181"/>
-      <c r="J11" s="180"/>
-      <c r="K11" s="181"/>
+      <c r="C11" s="195"/>
+      <c r="D11" s="196"/>
+      <c r="E11" s="197"/>
+      <c r="F11" s="167"/>
+      <c r="G11" s="168"/>
+      <c r="H11" s="181"/>
+      <c r="I11" s="182"/>
+      <c r="J11" s="181"/>
+      <c r="K11" s="182"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
     </row>
@@ -3827,17 +3827,17 @@
       <c r="B12" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="177" t="s">
+      <c r="C12" s="198" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="178"/>
-      <c r="E12" s="179"/>
-      <c r="F12" s="202"/>
-      <c r="G12" s="203"/>
-      <c r="H12" s="180"/>
-      <c r="I12" s="181"/>
-      <c r="J12" s="180"/>
-      <c r="K12" s="181"/>
+      <c r="D12" s="199"/>
+      <c r="E12" s="200"/>
+      <c r="F12" s="167"/>
+      <c r="G12" s="168"/>
+      <c r="H12" s="181"/>
+      <c r="I12" s="182"/>
+      <c r="J12" s="181"/>
+      <c r="K12" s="182"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
     </row>
@@ -3846,15 +3846,15 @@
       <c r="B13" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="182"/>
-      <c r="D13" s="183"/>
-      <c r="E13" s="184"/>
-      <c r="F13" s="204"/>
-      <c r="G13" s="205"/>
-      <c r="H13" s="180"/>
-      <c r="I13" s="181"/>
-      <c r="J13" s="180"/>
-      <c r="K13" s="181"/>
+      <c r="C13" s="195"/>
+      <c r="D13" s="196"/>
+      <c r="E13" s="197"/>
+      <c r="F13" s="169"/>
+      <c r="G13" s="170"/>
+      <c r="H13" s="181"/>
+      <c r="I13" s="182"/>
+      <c r="J13" s="181"/>
+      <c r="K13" s="182"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
     </row>
@@ -3863,17 +3863,17 @@
       <c r="B14" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="163"/>
-      <c r="D14" s="163"/>
-      <c r="E14" s="164"/>
-      <c r="F14" s="165" t="s">
+      <c r="C14" s="201"/>
+      <c r="D14" s="201"/>
+      <c r="E14" s="202"/>
+      <c r="F14" s="203" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="166"/>
-      <c r="H14" s="169" t="s">
+      <c r="G14" s="204"/>
+      <c r="H14" s="207" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="170"/>
+      <c r="I14" s="208"/>
       <c r="J14" s="17"/>
       <c r="K14" s="18"/>
       <c r="L14" s="4"/>
@@ -3891,14 +3891,14 @@
       <c r="E15" s="16">
         <v>1</v>
       </c>
-      <c r="F15" s="167"/>
-      <c r="G15" s="168"/>
-      <c r="H15" s="167"/>
-      <c r="I15" s="171"/>
-      <c r="J15" s="172" t="s">
+      <c r="F15" s="205"/>
+      <c r="G15" s="206"/>
+      <c r="H15" s="205"/>
+      <c r="I15" s="209"/>
+      <c r="J15" s="210" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="174" t="s">
+      <c r="K15" s="212" t="s">
         <v>20</v>
       </c>
       <c r="L15" s="4"/>
@@ -3924,12 +3924,12 @@
       <c r="G16" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="176" t="s">
+      <c r="H16" s="214" t="s">
         <v>26</v>
       </c>
-      <c r="I16" s="176"/>
-      <c r="J16" s="173"/>
-      <c r="K16" s="175"/>
+      <c r="I16" s="214"/>
+      <c r="J16" s="211"/>
+      <c r="K16" s="213"/>
       <c r="L16" s="25"/>
       <c r="M16" s="25"/>
     </row>
@@ -3938,15 +3938,15 @@
       <c r="B17" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="156" t="s">
+      <c r="C17" s="215" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="157"/>
-      <c r="E17" s="157"/>
-      <c r="F17" s="157"/>
-      <c r="G17" s="157"/>
-      <c r="H17" s="157"/>
-      <c r="I17" s="158"/>
+      <c r="D17" s="216"/>
+      <c r="E17" s="216"/>
+      <c r="F17" s="216"/>
+      <c r="G17" s="216"/>
+      <c r="H17" s="216"/>
+      <c r="I17" s="217"/>
       <c r="J17" s="40"/>
       <c r="K17" s="41"/>
       <c r="L17" s="25"/>
@@ -4021,10 +4021,10 @@
       <c r="G21" s="57" t="s">
         <v>37</v>
       </c>
-      <c r="H21" s="159" t="s">
+      <c r="H21" s="218" t="s">
         <v>38</v>
       </c>
-      <c r="I21" s="160"/>
+      <c r="I21" s="219"/>
       <c r="J21" s="40"/>
       <c r="K21" s="41"/>
       <c r="L21" s="25"/>
@@ -4048,10 +4048,10 @@
       <c r="G22" s="57" t="s">
         <v>37</v>
       </c>
-      <c r="H22" s="159" t="s">
+      <c r="H22" s="218" t="s">
         <v>41</v>
       </c>
-      <c r="I22" s="160"/>
+      <c r="I22" s="219"/>
       <c r="J22" s="40"/>
       <c r="K22" s="41"/>
       <c r="L22" s="25"/>
@@ -4092,10 +4092,10 @@
       <c r="G24" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="H24" s="146" t="s">
+      <c r="H24" s="221" t="s">
         <v>43</v>
       </c>
-      <c r="I24" s="146"/>
+      <c r="I24" s="221"/>
       <c r="J24" s="40"/>
       <c r="K24" s="41"/>
       <c r="L24" s="25"/>
@@ -4132,10 +4132,10 @@
       <c r="G26" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H26" s="146" t="s">
+      <c r="H26" s="221" t="s">
         <v>45</v>
       </c>
-      <c r="I26" s="146"/>
+      <c r="I26" s="221"/>
       <c r="J26" s="40"/>
       <c r="K26" s="75"/>
       <c r="L26" s="25"/>
@@ -4159,10 +4159,10 @@
       <c r="G27" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H27" s="150" t="s">
+      <c r="H27" s="145" t="s">
         <v>47</v>
       </c>
-      <c r="I27" s="150"/>
+      <c r="I27" s="145"/>
       <c r="J27" s="76"/>
       <c r="K27" s="77"/>
       <c r="L27" s="25"/>
@@ -4188,10 +4188,10 @@
       <c r="G28" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="H28" s="150" t="s">
+      <c r="H28" s="145" t="s">
         <v>50</v>
       </c>
-      <c r="I28" s="150"/>
+      <c r="I28" s="145"/>
       <c r="J28" s="76"/>
       <c r="K28" s="77"/>
       <c r="L28" s="25"/>
@@ -4228,10 +4228,10 @@
       <c r="G30" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H30" s="146" t="s">
+      <c r="H30" s="221" t="s">
         <v>45</v>
       </c>
-      <c r="I30" s="146"/>
+      <c r="I30" s="221"/>
       <c r="J30" s="40"/>
       <c r="K30" s="75"/>
       <c r="L30" s="25"/>
@@ -4249,10 +4249,10 @@
       <c r="G31" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H31" s="150" t="s">
+      <c r="H31" s="145" t="s">
         <v>47</v>
       </c>
-      <c r="I31" s="150"/>
+      <c r="I31" s="145"/>
       <c r="J31" s="40"/>
       <c r="K31" s="75"/>
       <c r="L31" s="25"/>
@@ -4278,10 +4278,10 @@
       <c r="G32" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="H32" s="150" t="s">
+      <c r="H32" s="145" t="s">
         <v>50</v>
       </c>
-      <c r="I32" s="150"/>
+      <c r="I32" s="145"/>
       <c r="J32" s="76"/>
       <c r="K32" s="77"/>
       <c r="L32" s="25"/>
@@ -4316,10 +4316,10 @@
       <c r="G34" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="H34" s="147" t="s">
+      <c r="H34" s="143" t="s">
         <v>53</v>
       </c>
-      <c r="I34" s="147"/>
+      <c r="I34" s="143"/>
       <c r="J34" s="76"/>
       <c r="K34" s="76"/>
       <c r="L34" s="25"/>
@@ -4341,8 +4341,8 @@
       </c>
       <c r="F35" s="76"/>
       <c r="G35" s="27"/>
-      <c r="H35" s="147"/>
-      <c r="I35" s="147"/>
+      <c r="H35" s="143"/>
+      <c r="I35" s="143"/>
       <c r="J35" s="76"/>
       <c r="K35" s="76"/>
       <c r="L35" s="25"/>
@@ -4383,10 +4383,10 @@
       <c r="G37" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="H37" s="142" t="s">
+      <c r="H37" s="148" t="s">
         <v>55</v>
       </c>
-      <c r="I37" s="143"/>
+      <c r="I37" s="149"/>
       <c r="J37" s="84"/>
       <c r="K37" s="84"/>
       <c r="L37" s="25"/>
@@ -4412,10 +4412,10 @@
       <c r="G38" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="H38" s="142" t="s">
+      <c r="H38" s="148" t="s">
         <v>57</v>
       </c>
-      <c r="I38" s="143"/>
+      <c r="I38" s="149"/>
       <c r="J38" s="84"/>
       <c r="K38" s="84"/>
       <c r="L38" s="25"/>
@@ -4454,10 +4454,10 @@
       <c r="G40" s="91" t="s">
         <v>37</v>
       </c>
-      <c r="H40" s="161" t="s">
+      <c r="H40" s="222" t="s">
         <v>59</v>
       </c>
-      <c r="I40" s="162"/>
+      <c r="I40" s="223"/>
       <c r="J40" s="41"/>
       <c r="K40" s="41"/>
       <c r="L40" s="25"/>
@@ -4479,8 +4479,8 @@
       </c>
       <c r="F41" s="41"/>
       <c r="G41" s="41"/>
-      <c r="H41" s="148"/>
-      <c r="I41" s="149"/>
+      <c r="H41" s="224"/>
+      <c r="I41" s="225"/>
       <c r="J41" s="41"/>
       <c r="K41" s="41"/>
       <c r="L41" s="25"/>
@@ -4489,15 +4489,15 @@
     <row r="42" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A42" s="26"/>
       <c r="B42" s="92"/>
-      <c r="C42" s="219" t="s">
+      <c r="C42" s="150" t="s">
         <v>60</v>
       </c>
-      <c r="D42" s="219"/>
-      <c r="E42" s="219"/>
-      <c r="F42" s="219"/>
-      <c r="G42" s="219"/>
-      <c r="H42" s="220"/>
-      <c r="I42" s="221"/>
+      <c r="D42" s="150"/>
+      <c r="E42" s="150"/>
+      <c r="F42" s="150"/>
+      <c r="G42" s="150"/>
+      <c r="H42" s="151"/>
+      <c r="I42" s="152"/>
       <c r="J42" s="93"/>
       <c r="K42" s="93"/>
       <c r="L42" s="25"/>
@@ -4519,10 +4519,10 @@
       <c r="G43" s="97" t="s">
         <v>37</v>
       </c>
-      <c r="H43" s="151" t="s">
+      <c r="H43" s="220" t="s">
         <v>62</v>
       </c>
-      <c r="I43" s="151"/>
+      <c r="I43" s="220"/>
       <c r="J43" s="97"/>
       <c r="K43" s="97"/>
       <c r="L43" s="25"/>
@@ -4542,10 +4542,10 @@
       <c r="G44" s="97" t="s">
         <v>64</v>
       </c>
-      <c r="H44" s="151" t="s">
+      <c r="H44" s="220" t="s">
         <v>65</v>
       </c>
-      <c r="I44" s="151"/>
+      <c r="I44" s="220"/>
       <c r="J44" s="97"/>
       <c r="K44" s="97"/>
       <c r="L44" s="25"/>
@@ -4563,8 +4563,8 @@
       <c r="E45" s="96"/>
       <c r="F45" s="97"/>
       <c r="G45" s="97"/>
-      <c r="H45" s="152"/>
-      <c r="I45" s="153"/>
+      <c r="H45" s="153"/>
+      <c r="I45" s="154"/>
       <c r="J45" s="97"/>
       <c r="K45" s="97"/>
       <c r="L45" s="25"/>
@@ -4582,8 +4582,8 @@
       <c r="E46" s="96"/>
       <c r="F46" s="97"/>
       <c r="G46" s="97"/>
-      <c r="H46" s="152"/>
-      <c r="I46" s="153"/>
+      <c r="H46" s="153"/>
+      <c r="I46" s="154"/>
       <c r="J46" s="97"/>
       <c r="K46" s="97"/>
       <c r="L46" s="25"/>
@@ -4593,11 +4593,11 @@
       <c r="A47" s="26"/>
       <c r="B47" s="94"/>
       <c r="C47" s="101"/>
-      <c r="D47" s="222" t="s">
+      <c r="D47" s="155" t="s">
         <v>67</v>
       </c>
-      <c r="E47" s="222"/>
-      <c r="F47" s="222"/>
+      <c r="E47" s="155"/>
+      <c r="F47" s="155"/>
       <c r="G47" s="100"/>
       <c r="H47" s="99"/>
       <c r="I47" s="100"/>
@@ -4611,15 +4611,15 @@
       <c r="B48" s="102" t="s">
         <v>68</v>
       </c>
-      <c r="C48" s="223" t="s">
+      <c r="C48" s="156" t="s">
         <v>69</v>
       </c>
-      <c r="D48" s="224"/>
-      <c r="E48" s="224"/>
-      <c r="F48" s="224"/>
-      <c r="G48" s="225"/>
-      <c r="H48" s="154"/>
-      <c r="I48" s="155"/>
+      <c r="D48" s="157"/>
+      <c r="E48" s="157"/>
+      <c r="F48" s="157"/>
+      <c r="G48" s="158"/>
+      <c r="H48" s="138"/>
+      <c r="I48" s="139"/>
       <c r="J48" s="65"/>
       <c r="K48" s="65"/>
       <c r="L48" s="25"/>
@@ -4639,10 +4639,10 @@
       <c r="G49" s="105" t="s">
         <v>37</v>
       </c>
-      <c r="H49" s="142" t="s">
+      <c r="H49" s="148" t="s">
         <v>71</v>
       </c>
-      <c r="I49" s="143"/>
+      <c r="I49" s="149"/>
       <c r="J49" s="105"/>
       <c r="K49" s="105"/>
       <c r="L49" s="25"/>
@@ -4660,10 +4660,10 @@
       <c r="G50" s="105" t="s">
         <v>37</v>
       </c>
-      <c r="H50" s="142" t="s">
+      <c r="H50" s="148" t="s">
         <v>72</v>
       </c>
-      <c r="I50" s="143"/>
+      <c r="I50" s="149"/>
       <c r="J50" s="105"/>
       <c r="K50" s="105"/>
       <c r="L50" s="25"/>
@@ -4677,8 +4677,8 @@
       <c r="E51" s="56"/>
       <c r="F51" s="76"/>
       <c r="G51" s="91"/>
-      <c r="H51" s="144"/>
-      <c r="I51" s="145"/>
+      <c r="H51" s="229"/>
+      <c r="I51" s="230"/>
       <c r="J51" s="76"/>
       <c r="K51" s="76"/>
       <c r="L51" s="25"/>
@@ -4687,12 +4687,12 @@
     <row r="52" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A52" s="26"/>
       <c r="B52" s="102"/>
-      <c r="C52" s="139" t="s">
+      <c r="C52" s="226" t="s">
         <v>73</v>
       </c>
-      <c r="D52" s="140"/>
-      <c r="E52" s="140"/>
-      <c r="F52" s="141"/>
+      <c r="D52" s="227"/>
+      <c r="E52" s="227"/>
+      <c r="F52" s="228"/>
       <c r="G52" s="103"/>
       <c r="H52" s="107"/>
       <c r="I52" s="108"/>
@@ -4717,10 +4717,10 @@
       <c r="G53" s="91" t="s">
         <v>37</v>
       </c>
-      <c r="H53" s="146" t="s">
+      <c r="H53" s="221" t="s">
         <v>71</v>
       </c>
-      <c r="I53" s="146"/>
+      <c r="I53" s="221"/>
       <c r="J53" s="40"/>
       <c r="K53" s="41"/>
       <c r="L53" s="25"/>
@@ -4738,10 +4738,10 @@
       <c r="G54" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="H54" s="150" t="s">
+      <c r="H54" s="145" t="s">
         <v>76</v>
       </c>
-      <c r="I54" s="150"/>
+      <c r="I54" s="145"/>
       <c r="J54" s="40"/>
       <c r="K54" s="41"/>
       <c r="L54" s="25"/>
@@ -4759,10 +4759,10 @@
       <c r="G55" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="H55" s="148" t="s">
+      <c r="H55" s="224" t="s">
         <v>72</v>
       </c>
-      <c r="I55" s="149"/>
+      <c r="I55" s="225"/>
       <c r="J55" s="40"/>
       <c r="K55" s="41"/>
       <c r="L55" s="25"/>
@@ -4776,8 +4776,8 @@
       <c r="E56" s="56"/>
       <c r="F56" s="76"/>
       <c r="G56" s="76"/>
-      <c r="H56" s="147"/>
-      <c r="I56" s="147"/>
+      <c r="H56" s="143"/>
+      <c r="I56" s="143"/>
       <c r="J56" s="84"/>
       <c r="K56" s="113"/>
       <c r="L56" s="25"/>
@@ -4818,10 +4818,10 @@
       <c r="G58" s="115" t="s">
         <v>37</v>
       </c>
-      <c r="H58" s="231" t="s">
+      <c r="H58" s="141" t="s">
         <v>59</v>
       </c>
-      <c r="I58" s="232"/>
+      <c r="I58" s="142"/>
       <c r="J58" s="41"/>
       <c r="K58" s="41"/>
       <c r="L58" s="4"/>
@@ -4843,8 +4843,8 @@
       </c>
       <c r="F59" s="76"/>
       <c r="G59" s="76"/>
-      <c r="H59" s="147"/>
-      <c r="I59" s="147"/>
+      <c r="H59" s="143"/>
+      <c r="I59" s="143"/>
       <c r="J59" s="27"/>
       <c r="K59" s="27"/>
       <c r="L59" s="4"/>
@@ -4885,10 +4885,10 @@
       <c r="G61" s="122" t="s">
         <v>37</v>
       </c>
-      <c r="H61" s="233" t="s">
+      <c r="H61" s="144" t="s">
         <v>78</v>
       </c>
-      <c r="I61" s="233"/>
+      <c r="I61" s="144"/>
       <c r="J61" s="41"/>
       <c r="K61" s="41"/>
       <c r="L61" s="4"/>
@@ -4912,10 +4912,10 @@
       <c r="G62" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="H62" s="150" t="s">
+      <c r="H62" s="145" t="s">
         <v>79</v>
       </c>
-      <c r="I62" s="150"/>
+      <c r="I62" s="145"/>
       <c r="J62" s="41"/>
       <c r="K62" s="41"/>
       <c r="L62" s="4"/>
@@ -4956,10 +4956,10 @@
       <c r="G64" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H64" s="226" t="s">
+      <c r="H64" s="134" t="s">
         <v>81</v>
       </c>
-      <c r="I64" s="226"/>
+      <c r="I64" s="134"/>
       <c r="J64" s="27"/>
       <c r="K64" s="27"/>
       <c r="L64" s="4"/>
@@ -4977,10 +4977,10 @@
       <c r="G65" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H65" s="234" t="s">
+      <c r="H65" s="146" t="s">
         <v>82</v>
       </c>
-      <c r="I65" s="234"/>
+      <c r="I65" s="146"/>
       <c r="J65" s="27"/>
       <c r="K65" s="27"/>
       <c r="L65" s="4"/>
@@ -5000,8 +5000,8 @@
       <c r="E66" s="56"/>
       <c r="F66" s="41"/>
       <c r="G66" s="41"/>
-      <c r="H66" s="235"/>
-      <c r="I66" s="235"/>
+      <c r="H66" s="147"/>
+      <c r="I66" s="147"/>
       <c r="J66" s="41"/>
       <c r="K66" s="41"/>
       <c r="L66" s="4"/>
@@ -5010,13 +5010,13 @@
     <row r="67" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A67" s="30"/>
       <c r="B67" s="102"/>
-      <c r="C67" s="227"/>
-      <c r="D67" s="228"/>
-      <c r="E67" s="228"/>
-      <c r="F67" s="228"/>
-      <c r="G67" s="229"/>
-      <c r="H67" s="154"/>
-      <c r="I67" s="155"/>
+      <c r="C67" s="135"/>
+      <c r="D67" s="136"/>
+      <c r="E67" s="136"/>
+      <c r="F67" s="136"/>
+      <c r="G67" s="137"/>
+      <c r="H67" s="138"/>
+      <c r="I67" s="139"/>
       <c r="J67" s="65"/>
       <c r="K67" s="65"/>
       <c r="L67" s="4"/>
@@ -5042,10 +5042,10 @@
       <c r="G68" s="76" t="s">
         <v>84</v>
       </c>
-      <c r="H68" s="142" t="s">
+      <c r="H68" s="148" t="s">
         <v>85</v>
       </c>
-      <c r="I68" s="143"/>
+      <c r="I68" s="149"/>
       <c r="J68" s="84"/>
       <c r="K68" s="113"/>
       <c r="L68" s="4"/>
@@ -5099,12 +5099,12 @@
       <c r="A71" s="30"/>
       <c r="B71" s="125"/>
       <c r="C71" s="126"/>
-      <c r="D71" s="230"/>
-      <c r="E71" s="230"/>
+      <c r="D71" s="140"/>
+      <c r="E71" s="140"/>
       <c r="F71" s="127"/>
       <c r="G71" s="127"/>
-      <c r="H71" s="136"/>
-      <c r="I71" s="136"/>
+      <c r="H71" s="233"/>
+      <c r="I71" s="233"/>
       <c r="J71" s="127"/>
       <c r="K71" s="127"/>
       <c r="L71" s="4"/>
@@ -5130,10 +5130,10 @@
       <c r="G72" s="91" t="s">
         <v>64</v>
       </c>
-      <c r="H72" s="137" t="s">
+      <c r="H72" s="234" t="s">
         <v>89</v>
       </c>
-      <c r="I72" s="137"/>
+      <c r="I72" s="234"/>
       <c r="J72" s="132"/>
       <c r="K72" s="133"/>
       <c r="L72" s="4"/>
@@ -5147,8 +5147,8 @@
       <c r="E73" s="29"/>
       <c r="F73" s="29"/>
       <c r="G73" s="29"/>
-      <c r="H73" s="138"/>
-      <c r="I73" s="138"/>
+      <c r="H73" s="235"/>
+      <c r="I73" s="235"/>
       <c r="J73" s="33"/>
       <c r="K73" s="29"/>
       <c r="L73" s="4"/>
@@ -5162,8 +5162,8 @@
       <c r="E74" s="28"/>
       <c r="F74" s="28"/>
       <c r="G74" s="28"/>
-      <c r="H74" s="134"/>
-      <c r="I74" s="135"/>
+      <c r="H74" s="231"/>
+      <c r="I74" s="232"/>
       <c r="J74" s="32"/>
       <c r="K74" s="35"/>
       <c r="L74" s="4"/>
@@ -5177,8 +5177,8 @@
       <c r="E75" s="28"/>
       <c r="F75" s="28"/>
       <c r="G75" s="28"/>
-      <c r="H75" s="134"/>
-      <c r="I75" s="135"/>
+      <c r="H75" s="231"/>
+      <c r="I75" s="232"/>
       <c r="J75" s="32"/>
       <c r="K75" s="35"/>
       <c r="L75" s="37"/>
@@ -5192,8 +5192,8 @@
       <c r="E76" s="28"/>
       <c r="F76" s="28"/>
       <c r="G76" s="28"/>
-      <c r="H76" s="134"/>
-      <c r="I76" s="135"/>
+      <c r="H76" s="231"/>
+      <c r="I76" s="232"/>
       <c r="J76" s="32"/>
       <c r="K76" s="35"/>
       <c r="L76" s="37"/>
@@ -5207,8 +5207,8 @@
       <c r="E77" s="28"/>
       <c r="F77" s="28"/>
       <c r="G77" s="28"/>
-      <c r="H77" s="134"/>
-      <c r="I77" s="135"/>
+      <c r="H77" s="231"/>
+      <c r="I77" s="232"/>
       <c r="J77" s="32"/>
       <c r="K77" s="35"/>
       <c r="L77" s="4"/>
@@ -5309,22 +5309,64 @@
     </row>
   </sheetData>
   <mergeCells count="90">
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="H65:I65"/>
-    <mergeCell ref="H66:I66"/>
-    <mergeCell ref="H68:I68"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="H77:I77"/>
+    <mergeCell ref="H71:I71"/>
+    <mergeCell ref="H72:I72"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="C52:F52"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="C17:I17"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="F14:G15"/>
+    <mergeCell ref="H14:I15"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="J7:K7"/>
     <mergeCell ref="C2:E2"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="H2:K2"/>
@@ -5341,64 +5383,22 @@
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="C8:E8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="F14:G15"/>
-    <mergeCell ref="H14:I15"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="K15:K16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="C17:I17"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="C52:F52"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="H56:I56"/>
-    <mergeCell ref="H55:I55"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="H77:I77"/>
-    <mergeCell ref="H71:I71"/>
-    <mergeCell ref="H72:I72"/>
-    <mergeCell ref="H73:I73"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="H65:I65"/>
+    <mergeCell ref="H66:I66"/>
+    <mergeCell ref="H68:I68"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>

--- a/DEVELOPMENT_ALL_OLD_NEW/H&M/HM.0657 - C-2+ BERAVLY LIGHT.xlsx
+++ b/DEVELOPMENT_ALL_OLD_NEW/H&M/HM.0657 - C-2+ BERAVLY LIGHT.xlsx
@@ -1871,17 +1871,65 @@
     <xf numFmtId="0" fontId="39" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="5" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="41" fillId="5" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="41" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="41" fillId="5" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="35" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="41" fillId="10" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="41" fillId="10" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="41" fillId="10" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="58" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="58" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1889,169 +1937,106 @@
     <xf numFmtId="0" fontId="13" fillId="5" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="5" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="3" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="39" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="46" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="41" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="42" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="58" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="8" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="6" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="8" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="3" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="37" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="29" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="23" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="26" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="28" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="29" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="4" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="4" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="4" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2078,142 +2063,157 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="6" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="7" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="8" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="30" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="9" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="31" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="10" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="32" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="8" fillId="3" borderId="11" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="12" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="13" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="21" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="14" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="15" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="18" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="14" fontId="8" fillId="3" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="38" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="39" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="23" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="24" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="25" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="35" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="26" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="46" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="27" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="40" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="41" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="36" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="27" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="42" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="22" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="9" fillId="4" borderId="30" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="4" borderId="31" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="8" fillId="4" borderId="32" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="51" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="6" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="48" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="37" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="3" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="3" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="3" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="41" fillId="5" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="41" fillId="5" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="41" fillId="5" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="45" fillId="5" borderId="51" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="3" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="41" fillId="10" borderId="58" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="41" fillId="10" borderId="19" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="41" fillId="10" borderId="20" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="54" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="55" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="5" borderId="51" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="53" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="51" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2510,15 +2510,18 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="ALL SAMPLES"/>
+      <sheetName val="Sheet2"/>
       <sheetName val="Sheet1"/>
+      <sheetName val="CUSTOMER"/>
       <sheetName val="DATA"/>
-      <sheetName val="CUSTOMER"/>
       <sheetName val="SABLON"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4">
         <row r="2">
           <cell r="B2" t="str">
             <v>BILAL</v>
@@ -2566,8 +2569,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -3634,21 +3636,21 @@
       <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="159">
+      <c r="C2" s="191">
         <v>46266</v>
       </c>
-      <c r="D2" s="160"/>
-      <c r="E2" s="161"/>
-      <c r="F2" s="159" t="s">
+      <c r="D2" s="192"/>
+      <c r="E2" s="193"/>
+      <c r="F2" s="191" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="160"/>
-      <c r="H2" s="162" t="s">
+      <c r="G2" s="192"/>
+      <c r="H2" s="194" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="163"/>
-      <c r="J2" s="163"/>
-      <c r="K2" s="164"/>
+      <c r="I2" s="195"/>
+      <c r="J2" s="195"/>
+      <c r="K2" s="196"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
     </row>
@@ -3657,17 +3659,17 @@
       <c r="B3" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="159" t="s">
+      <c r="C3" s="191" t="s">
         <v>90</v>
       </c>
-      <c r="D3" s="160"/>
-      <c r="E3" s="161"/>
-      <c r="F3" s="165"/>
-      <c r="G3" s="166"/>
-      <c r="H3" s="171" t="s">
+      <c r="D3" s="192"/>
+      <c r="E3" s="193"/>
+      <c r="F3" s="197"/>
+      <c r="G3" s="198"/>
+      <c r="H3" s="203" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="172"/>
+      <c r="I3" s="204"/>
       <c r="J3" s="7"/>
       <c r="K3" s="8"/>
       <c r="L3" s="4"/>
@@ -3681,17 +3683,17 @@
       <c r="B4" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="173" t="s">
+      <c r="C4" s="205" t="s">
         <v>29</v>
       </c>
-      <c r="D4" s="174"/>
-      <c r="E4" s="175"/>
-      <c r="F4" s="167"/>
-      <c r="G4" s="168"/>
-      <c r="H4" s="176"/>
-      <c r="I4" s="177"/>
-      <c r="J4" s="176"/>
-      <c r="K4" s="177"/>
+      <c r="D4" s="206"/>
+      <c r="E4" s="207"/>
+      <c r="F4" s="199"/>
+      <c r="G4" s="200"/>
+      <c r="H4" s="208"/>
+      <c r="I4" s="209"/>
+      <c r="J4" s="208"/>
+      <c r="K4" s="209"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
     </row>
@@ -3700,17 +3702,17 @@
       <c r="B5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="178">
+      <c r="C5" s="210">
         <v>512241880</v>
       </c>
-      <c r="D5" s="179"/>
-      <c r="E5" s="180"/>
-      <c r="F5" s="167"/>
-      <c r="G5" s="168"/>
-      <c r="H5" s="181"/>
-      <c r="I5" s="182"/>
-      <c r="J5" s="181"/>
-      <c r="K5" s="182"/>
+      <c r="D5" s="211"/>
+      <c r="E5" s="212"/>
+      <c r="F5" s="199"/>
+      <c r="G5" s="200"/>
+      <c r="H5" s="180"/>
+      <c r="I5" s="181"/>
+      <c r="J5" s="180"/>
+      <c r="K5" s="181"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
     </row>
@@ -3719,17 +3721,17 @@
       <c r="B6" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="183" t="s">
+      <c r="C6" s="213" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="184"/>
-      <c r="E6" s="185"/>
-      <c r="F6" s="167"/>
-      <c r="G6" s="168"/>
-      <c r="H6" s="181"/>
-      <c r="I6" s="182"/>
-      <c r="J6" s="181"/>
-      <c r="K6" s="182"/>
+      <c r="D6" s="214"/>
+      <c r="E6" s="215"/>
+      <c r="F6" s="199"/>
+      <c r="G6" s="200"/>
+      <c r="H6" s="180"/>
+      <c r="I6" s="181"/>
+      <c r="J6" s="180"/>
+      <c r="K6" s="181"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
     </row>
@@ -3738,17 +3740,17 @@
       <c r="B7" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="192" t="s">
+      <c r="C7" s="188" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="193"/>
-      <c r="E7" s="194"/>
-      <c r="F7" s="167"/>
-      <c r="G7" s="168"/>
-      <c r="H7" s="181"/>
-      <c r="I7" s="182"/>
-      <c r="J7" s="181"/>
-      <c r="K7" s="182"/>
+      <c r="D7" s="189"/>
+      <c r="E7" s="190"/>
+      <c r="F7" s="199"/>
+      <c r="G7" s="200"/>
+      <c r="H7" s="180"/>
+      <c r="I7" s="181"/>
+      <c r="J7" s="180"/>
+      <c r="K7" s="181"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
     </row>
@@ -3757,15 +3759,15 @@
       <c r="B8" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="186"/>
-      <c r="D8" s="187"/>
-      <c r="E8" s="188"/>
-      <c r="F8" s="167"/>
-      <c r="G8" s="168"/>
+      <c r="C8" s="216"/>
+      <c r="D8" s="217"/>
+      <c r="E8" s="218"/>
+      <c r="F8" s="199"/>
+      <c r="G8" s="200"/>
       <c r="H8" s="11"/>
       <c r="I8" s="12"/>
-      <c r="J8" s="181"/>
-      <c r="K8" s="182"/>
+      <c r="J8" s="180"/>
+      <c r="K8" s="181"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
     </row>
@@ -3774,17 +3776,17 @@
       <c r="B9" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="189">
+      <c r="C9" s="185">
         <v>5</v>
       </c>
-      <c r="D9" s="190"/>
-      <c r="E9" s="191"/>
-      <c r="F9" s="167"/>
-      <c r="G9" s="168"/>
+      <c r="D9" s="186"/>
+      <c r="E9" s="187"/>
+      <c r="F9" s="199"/>
+      <c r="G9" s="200"/>
       <c r="H9" s="11"/>
       <c r="I9" s="12"/>
-      <c r="J9" s="181"/>
-      <c r="K9" s="182"/>
+      <c r="J9" s="180"/>
+      <c r="K9" s="181"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
     </row>
@@ -3793,15 +3795,15 @@
       <c r="B10" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="189"/>
-      <c r="D10" s="190"/>
-      <c r="E10" s="191"/>
-      <c r="F10" s="167"/>
-      <c r="G10" s="168"/>
+      <c r="C10" s="185"/>
+      <c r="D10" s="186"/>
+      <c r="E10" s="187"/>
+      <c r="F10" s="199"/>
+      <c r="G10" s="200"/>
       <c r="H10" s="11"/>
       <c r="I10" s="12"/>
-      <c r="J10" s="181"/>
-      <c r="K10" s="182"/>
+      <c r="J10" s="180"/>
+      <c r="K10" s="181"/>
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
     </row>
@@ -3810,15 +3812,15 @@
       <c r="B11" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="195"/>
-      <c r="D11" s="196"/>
-      <c r="E11" s="197"/>
-      <c r="F11" s="167"/>
-      <c r="G11" s="168"/>
-      <c r="H11" s="181"/>
-      <c r="I11" s="182"/>
-      <c r="J11" s="181"/>
-      <c r="K11" s="182"/>
+      <c r="C11" s="182"/>
+      <c r="D11" s="183"/>
+      <c r="E11" s="184"/>
+      <c r="F11" s="199"/>
+      <c r="G11" s="200"/>
+      <c r="H11" s="180"/>
+      <c r="I11" s="181"/>
+      <c r="J11" s="180"/>
+      <c r="K11" s="181"/>
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
     </row>
@@ -3827,17 +3829,17 @@
       <c r="B12" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="198" t="s">
+      <c r="C12" s="177" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="199"/>
-      <c r="E12" s="200"/>
-      <c r="F12" s="167"/>
-      <c r="G12" s="168"/>
-      <c r="H12" s="181"/>
-      <c r="I12" s="182"/>
-      <c r="J12" s="181"/>
-      <c r="K12" s="182"/>
+      <c r="D12" s="178"/>
+      <c r="E12" s="179"/>
+      <c r="F12" s="199"/>
+      <c r="G12" s="200"/>
+      <c r="H12" s="180"/>
+      <c r="I12" s="181"/>
+      <c r="J12" s="180"/>
+      <c r="K12" s="181"/>
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
     </row>
@@ -3846,15 +3848,15 @@
       <c r="B13" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="195"/>
-      <c r="D13" s="196"/>
-      <c r="E13" s="197"/>
-      <c r="F13" s="169"/>
-      <c r="G13" s="170"/>
-      <c r="H13" s="181"/>
-      <c r="I13" s="182"/>
-      <c r="J13" s="181"/>
-      <c r="K13" s="182"/>
+      <c r="C13" s="182"/>
+      <c r="D13" s="183"/>
+      <c r="E13" s="184"/>
+      <c r="F13" s="201"/>
+      <c r="G13" s="202"/>
+      <c r="H13" s="180"/>
+      <c r="I13" s="181"/>
+      <c r="J13" s="180"/>
+      <c r="K13" s="181"/>
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
     </row>
@@ -3863,17 +3865,17 @@
       <c r="B14" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="201"/>
-      <c r="D14" s="201"/>
-      <c r="E14" s="202"/>
-      <c r="F14" s="203" t="s">
+      <c r="C14" s="163"/>
+      <c r="D14" s="163"/>
+      <c r="E14" s="164"/>
+      <c r="F14" s="165" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="204"/>
-      <c r="H14" s="207" t="s">
+      <c r="G14" s="166"/>
+      <c r="H14" s="169" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="208"/>
+      <c r="I14" s="170"/>
       <c r="J14" s="17"/>
       <c r="K14" s="18"/>
       <c r="L14" s="4"/>
@@ -3891,14 +3893,14 @@
       <c r="E15" s="16">
         <v>1</v>
       </c>
-      <c r="F15" s="205"/>
-      <c r="G15" s="206"/>
-      <c r="H15" s="205"/>
-      <c r="I15" s="209"/>
-      <c r="J15" s="210" t="s">
+      <c r="F15" s="167"/>
+      <c r="G15" s="168"/>
+      <c r="H15" s="167"/>
+      <c r="I15" s="171"/>
+      <c r="J15" s="172" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="212" t="s">
+      <c r="K15" s="174" t="s">
         <v>20</v>
       </c>
       <c r="L15" s="4"/>
@@ -3924,12 +3926,12 @@
       <c r="G16" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="214" t="s">
+      <c r="H16" s="176" t="s">
         <v>26</v>
       </c>
-      <c r="I16" s="214"/>
-      <c r="J16" s="211"/>
-      <c r="K16" s="213"/>
+      <c r="I16" s="176"/>
+      <c r="J16" s="173"/>
+      <c r="K16" s="175"/>
       <c r="L16" s="25"/>
       <c r="M16" s="25"/>
     </row>
@@ -3938,15 +3940,15 @@
       <c r="B17" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="215" t="s">
+      <c r="C17" s="156" t="s">
         <v>27</v>
       </c>
-      <c r="D17" s="216"/>
-      <c r="E17" s="216"/>
-      <c r="F17" s="216"/>
-      <c r="G17" s="216"/>
-      <c r="H17" s="216"/>
-      <c r="I17" s="217"/>
+      <c r="D17" s="157"/>
+      <c r="E17" s="157"/>
+      <c r="F17" s="157"/>
+      <c r="G17" s="157"/>
+      <c r="H17" s="157"/>
+      <c r="I17" s="158"/>
       <c r="J17" s="40"/>
       <c r="K17" s="41"/>
       <c r="L17" s="25"/>
@@ -4021,10 +4023,10 @@
       <c r="G21" s="57" t="s">
         <v>37</v>
       </c>
-      <c r="H21" s="218" t="s">
+      <c r="H21" s="159" t="s">
         <v>38</v>
       </c>
-      <c r="I21" s="219"/>
+      <c r="I21" s="160"/>
       <c r="J21" s="40"/>
       <c r="K21" s="41"/>
       <c r="L21" s="25"/>
@@ -4048,10 +4050,10 @@
       <c r="G22" s="57" t="s">
         <v>37</v>
       </c>
-      <c r="H22" s="218" t="s">
+      <c r="H22" s="159" t="s">
         <v>41</v>
       </c>
-      <c r="I22" s="219"/>
+      <c r="I22" s="160"/>
       <c r="J22" s="40"/>
       <c r="K22" s="41"/>
       <c r="L22" s="25"/>
@@ -4092,10 +4094,10 @@
       <c r="G24" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="H24" s="221" t="s">
+      <c r="H24" s="146" t="s">
         <v>43</v>
       </c>
-      <c r="I24" s="221"/>
+      <c r="I24" s="146"/>
       <c r="J24" s="40"/>
       <c r="K24" s="41"/>
       <c r="L24" s="25"/>
@@ -4132,10 +4134,10 @@
       <c r="G26" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H26" s="221" t="s">
+      <c r="H26" s="146" t="s">
         <v>45</v>
       </c>
-      <c r="I26" s="221"/>
+      <c r="I26" s="146"/>
       <c r="J26" s="40"/>
       <c r="K26" s="75"/>
       <c r="L26" s="25"/>
@@ -4159,10 +4161,10 @@
       <c r="G27" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H27" s="145" t="s">
+      <c r="H27" s="150" t="s">
         <v>47</v>
       </c>
-      <c r="I27" s="145"/>
+      <c r="I27" s="150"/>
       <c r="J27" s="76"/>
       <c r="K27" s="77"/>
       <c r="L27" s="25"/>
@@ -4188,10 +4190,10 @@
       <c r="G28" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="H28" s="145" t="s">
+      <c r="H28" s="150" t="s">
         <v>50</v>
       </c>
-      <c r="I28" s="145"/>
+      <c r="I28" s="150"/>
       <c r="J28" s="76"/>
       <c r="K28" s="77"/>
       <c r="L28" s="25"/>
@@ -4228,10 +4230,10 @@
       <c r="G30" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H30" s="221" t="s">
+      <c r="H30" s="146" t="s">
         <v>45</v>
       </c>
-      <c r="I30" s="221"/>
+      <c r="I30" s="146"/>
       <c r="J30" s="40"/>
       <c r="K30" s="75"/>
       <c r="L30" s="25"/>
@@ -4249,10 +4251,10 @@
       <c r="G31" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H31" s="145" t="s">
+      <c r="H31" s="150" t="s">
         <v>47</v>
       </c>
-      <c r="I31" s="145"/>
+      <c r="I31" s="150"/>
       <c r="J31" s="40"/>
       <c r="K31" s="75"/>
       <c r="L31" s="25"/>
@@ -4278,10 +4280,10 @@
       <c r="G32" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="H32" s="145" t="s">
+      <c r="H32" s="150" t="s">
         <v>50</v>
       </c>
-      <c r="I32" s="145"/>
+      <c r="I32" s="150"/>
       <c r="J32" s="76"/>
       <c r="K32" s="77"/>
       <c r="L32" s="25"/>
@@ -4316,10 +4318,10 @@
       <c r="G34" s="76" t="s">
         <v>37</v>
       </c>
-      <c r="H34" s="143" t="s">
+      <c r="H34" s="147" t="s">
         <v>53</v>
       </c>
-      <c r="I34" s="143"/>
+      <c r="I34" s="147"/>
       <c r="J34" s="76"/>
       <c r="K34" s="76"/>
       <c r="L34" s="25"/>
@@ -4341,8 +4343,8 @@
       </c>
       <c r="F35" s="76"/>
       <c r="G35" s="27"/>
-      <c r="H35" s="143"/>
-      <c r="I35" s="143"/>
+      <c r="H35" s="147"/>
+      <c r="I35" s="147"/>
       <c r="J35" s="76"/>
       <c r="K35" s="76"/>
       <c r="L35" s="25"/>
@@ -4383,10 +4385,10 @@
       <c r="G37" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="H37" s="148" t="s">
+      <c r="H37" s="142" t="s">
         <v>55</v>
       </c>
-      <c r="I37" s="149"/>
+      <c r="I37" s="143"/>
       <c r="J37" s="84"/>
       <c r="K37" s="84"/>
       <c r="L37" s="25"/>
@@ -4412,10 +4414,10 @@
       <c r="G38" s="85" t="s">
         <v>37</v>
       </c>
-      <c r="H38" s="148" t="s">
+      <c r="H38" s="142" t="s">
         <v>57</v>
       </c>
-      <c r="I38" s="149"/>
+      <c r="I38" s="143"/>
       <c r="J38" s="84"/>
       <c r="K38" s="84"/>
       <c r="L38" s="25"/>
@@ -4454,10 +4456,10 @@
       <c r="G40" s="91" t="s">
         <v>37</v>
       </c>
-      <c r="H40" s="222" t="s">
+      <c r="H40" s="161" t="s">
         <v>59</v>
       </c>
-      <c r="I40" s="223"/>
+      <c r="I40" s="162"/>
       <c r="J40" s="41"/>
       <c r="K40" s="41"/>
       <c r="L40" s="25"/>
@@ -4479,8 +4481,8 @@
       </c>
       <c r="F41" s="41"/>
       <c r="G41" s="41"/>
-      <c r="H41" s="224"/>
-      <c r="I41" s="225"/>
+      <c r="H41" s="148"/>
+      <c r="I41" s="149"/>
       <c r="J41" s="41"/>
       <c r="K41" s="41"/>
       <c r="L41" s="25"/>
@@ -4489,15 +4491,15 @@
     <row r="42" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A42" s="26"/>
       <c r="B42" s="92"/>
-      <c r="C42" s="150" t="s">
+      <c r="C42" s="219" t="s">
         <v>60</v>
       </c>
-      <c r="D42" s="150"/>
-      <c r="E42" s="150"/>
-      <c r="F42" s="150"/>
-      <c r="G42" s="150"/>
-      <c r="H42" s="151"/>
-      <c r="I42" s="152"/>
+      <c r="D42" s="219"/>
+      <c r="E42" s="219"/>
+      <c r="F42" s="219"/>
+      <c r="G42" s="219"/>
+      <c r="H42" s="220"/>
+      <c r="I42" s="221"/>
       <c r="J42" s="93"/>
       <c r="K42" s="93"/>
       <c r="L42" s="25"/>
@@ -4519,10 +4521,10 @@
       <c r="G43" s="97" t="s">
         <v>37</v>
       </c>
-      <c r="H43" s="220" t="s">
+      <c r="H43" s="151" t="s">
         <v>62</v>
       </c>
-      <c r="I43" s="220"/>
+      <c r="I43" s="151"/>
       <c r="J43" s="97"/>
       <c r="K43" s="97"/>
       <c r="L43" s="25"/>
@@ -4542,10 +4544,10 @@
       <c r="G44" s="97" t="s">
         <v>64</v>
       </c>
-      <c r="H44" s="220" t="s">
+      <c r="H44" s="151" t="s">
         <v>65</v>
       </c>
-      <c r="I44" s="220"/>
+      <c r="I44" s="151"/>
       <c r="J44" s="97"/>
       <c r="K44" s="97"/>
       <c r="L44" s="25"/>
@@ -4563,8 +4565,8 @@
       <c r="E45" s="96"/>
       <c r="F45" s="97"/>
       <c r="G45" s="97"/>
-      <c r="H45" s="153"/>
-      <c r="I45" s="154"/>
+      <c r="H45" s="152"/>
+      <c r="I45" s="153"/>
       <c r="J45" s="97"/>
       <c r="K45" s="97"/>
       <c r="L45" s="25"/>
@@ -4582,8 +4584,8 @@
       <c r="E46" s="96"/>
       <c r="F46" s="97"/>
       <c r="G46" s="97"/>
-      <c r="H46" s="153"/>
-      <c r="I46" s="154"/>
+      <c r="H46" s="152"/>
+      <c r="I46" s="153"/>
       <c r="J46" s="97"/>
       <c r="K46" s="97"/>
       <c r="L46" s="25"/>
@@ -4593,11 +4595,11 @@
       <c r="A47" s="26"/>
       <c r="B47" s="94"/>
       <c r="C47" s="101"/>
-      <c r="D47" s="155" t="s">
+      <c r="D47" s="222" t="s">
         <v>67</v>
       </c>
-      <c r="E47" s="155"/>
-      <c r="F47" s="155"/>
+      <c r="E47" s="222"/>
+      <c r="F47" s="222"/>
       <c r="G47" s="100"/>
       <c r="H47" s="99"/>
       <c r="I47" s="100"/>
@@ -4611,15 +4613,15 @@
       <c r="B48" s="102" t="s">
         <v>68</v>
       </c>
-      <c r="C48" s="156" t="s">
+      <c r="C48" s="223" t="s">
         <v>69</v>
       </c>
-      <c r="D48" s="157"/>
-      <c r="E48" s="157"/>
-      <c r="F48" s="157"/>
-      <c r="G48" s="158"/>
-      <c r="H48" s="138"/>
-      <c r="I48" s="139"/>
+      <c r="D48" s="224"/>
+      <c r="E48" s="224"/>
+      <c r="F48" s="224"/>
+      <c r="G48" s="225"/>
+      <c r="H48" s="154"/>
+      <c r="I48" s="155"/>
       <c r="J48" s="65"/>
       <c r="K48" s="65"/>
       <c r="L48" s="25"/>
@@ -4639,10 +4641,10 @@
       <c r="G49" s="105" t="s">
         <v>37</v>
       </c>
-      <c r="H49" s="148" t="s">
+      <c r="H49" s="142" t="s">
         <v>71</v>
       </c>
-      <c r="I49" s="149"/>
+      <c r="I49" s="143"/>
       <c r="J49" s="105"/>
       <c r="K49" s="105"/>
       <c r="L49" s="25"/>
@@ -4660,10 +4662,10 @@
       <c r="G50" s="105" t="s">
         <v>37</v>
       </c>
-      <c r="H50" s="148" t="s">
+      <c r="H50" s="142" t="s">
         <v>72</v>
       </c>
-      <c r="I50" s="149"/>
+      <c r="I50" s="143"/>
       <c r="J50" s="105"/>
       <c r="K50" s="105"/>
       <c r="L50" s="25"/>
@@ -4677,8 +4679,8 @@
       <c r="E51" s="56"/>
       <c r="F51" s="76"/>
       <c r="G51" s="91"/>
-      <c r="H51" s="229"/>
-      <c r="I51" s="230"/>
+      <c r="H51" s="144"/>
+      <c r="I51" s="145"/>
       <c r="J51" s="76"/>
       <c r="K51" s="76"/>
       <c r="L51" s="25"/>
@@ -4687,12 +4689,12 @@
     <row r="52" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A52" s="26"/>
       <c r="B52" s="102"/>
-      <c r="C52" s="226" t="s">
+      <c r="C52" s="139" t="s">
         <v>73</v>
       </c>
-      <c r="D52" s="227"/>
-      <c r="E52" s="227"/>
-      <c r="F52" s="228"/>
+      <c r="D52" s="140"/>
+      <c r="E52" s="140"/>
+      <c r="F52" s="141"/>
       <c r="G52" s="103"/>
       <c r="H52" s="107"/>
       <c r="I52" s="108"/>
@@ -4717,10 +4719,10 @@
       <c r="G53" s="91" t="s">
         <v>37</v>
       </c>
-      <c r="H53" s="221" t="s">
+      <c r="H53" s="146" t="s">
         <v>71</v>
       </c>
-      <c r="I53" s="221"/>
+      <c r="I53" s="146"/>
       <c r="J53" s="40"/>
       <c r="K53" s="41"/>
       <c r="L53" s="25"/>
@@ -4738,10 +4740,10 @@
       <c r="G54" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="H54" s="145" t="s">
+      <c r="H54" s="150" t="s">
         <v>76</v>
       </c>
-      <c r="I54" s="145"/>
+      <c r="I54" s="150"/>
       <c r="J54" s="40"/>
       <c r="K54" s="41"/>
       <c r="L54" s="25"/>
@@ -4759,10 +4761,10 @@
       <c r="G55" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="H55" s="224" t="s">
+      <c r="H55" s="148" t="s">
         <v>72</v>
       </c>
-      <c r="I55" s="225"/>
+      <c r="I55" s="149"/>
       <c r="J55" s="40"/>
       <c r="K55" s="41"/>
       <c r="L55" s="25"/>
@@ -4776,8 +4778,8 @@
       <c r="E56" s="56"/>
       <c r="F56" s="76"/>
       <c r="G56" s="76"/>
-      <c r="H56" s="143"/>
-      <c r="I56" s="143"/>
+      <c r="H56" s="147"/>
+      <c r="I56" s="147"/>
       <c r="J56" s="84"/>
       <c r="K56" s="113"/>
       <c r="L56" s="25"/>
@@ -4818,10 +4820,10 @@
       <c r="G58" s="115" t="s">
         <v>37</v>
       </c>
-      <c r="H58" s="141" t="s">
+      <c r="H58" s="231" t="s">
         <v>59</v>
       </c>
-      <c r="I58" s="142"/>
+      <c r="I58" s="232"/>
       <c r="J58" s="41"/>
       <c r="K58" s="41"/>
       <c r="L58" s="4"/>
@@ -4843,8 +4845,8 @@
       </c>
       <c r="F59" s="76"/>
       <c r="G59" s="76"/>
-      <c r="H59" s="143"/>
-      <c r="I59" s="143"/>
+      <c r="H59" s="147"/>
+      <c r="I59" s="147"/>
       <c r="J59" s="27"/>
       <c r="K59" s="27"/>
       <c r="L59" s="4"/>
@@ -4885,10 +4887,10 @@
       <c r="G61" s="122" t="s">
         <v>37</v>
       </c>
-      <c r="H61" s="144" t="s">
+      <c r="H61" s="233" t="s">
         <v>78</v>
       </c>
-      <c r="I61" s="144"/>
+      <c r="I61" s="233"/>
       <c r="J61" s="41"/>
       <c r="K61" s="41"/>
       <c r="L61" s="4"/>
@@ -4912,10 +4914,10 @@
       <c r="G62" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="H62" s="145" t="s">
+      <c r="H62" s="150" t="s">
         <v>79</v>
       </c>
-      <c r="I62" s="145"/>
+      <c r="I62" s="150"/>
       <c r="J62" s="41"/>
       <c r="K62" s="41"/>
       <c r="L62" s="4"/>
@@ -4956,10 +4958,10 @@
       <c r="G64" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H64" s="134" t="s">
+      <c r="H64" s="226" t="s">
         <v>81</v>
       </c>
-      <c r="I64" s="134"/>
+      <c r="I64" s="226"/>
       <c r="J64" s="27"/>
       <c r="K64" s="27"/>
       <c r="L64" s="4"/>
@@ -4977,10 +4979,10 @@
       <c r="G65" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="H65" s="146" t="s">
+      <c r="H65" s="234" t="s">
         <v>82</v>
       </c>
-      <c r="I65" s="146"/>
+      <c r="I65" s="234"/>
       <c r="J65" s="27"/>
       <c r="K65" s="27"/>
       <c r="L65" s="4"/>
@@ -5000,8 +5002,8 @@
       <c r="E66" s="56"/>
       <c r="F66" s="41"/>
       <c r="G66" s="41"/>
-      <c r="H66" s="147"/>
-      <c r="I66" s="147"/>
+      <c r="H66" s="235"/>
+      <c r="I66" s="235"/>
       <c r="J66" s="41"/>
       <c r="K66" s="41"/>
       <c r="L66" s="4"/>
@@ -5010,13 +5012,13 @@
     <row r="67" spans="1:13" ht="74.099999999999994" customHeight="1">
       <c r="A67" s="30"/>
       <c r="B67" s="102"/>
-      <c r="C67" s="135"/>
-      <c r="D67" s="136"/>
-      <c r="E67" s="136"/>
-      <c r="F67" s="136"/>
-      <c r="G67" s="137"/>
-      <c r="H67" s="138"/>
-      <c r="I67" s="139"/>
+      <c r="C67" s="227"/>
+      <c r="D67" s="228"/>
+      <c r="E67" s="228"/>
+      <c r="F67" s="228"/>
+      <c r="G67" s="229"/>
+      <c r="H67" s="154"/>
+      <c r="I67" s="155"/>
       <c r="J67" s="65"/>
       <c r="K67" s="65"/>
       <c r="L67" s="4"/>
@@ -5042,10 +5044,10 @@
       <c r="G68" s="76" t="s">
         <v>84</v>
       </c>
-      <c r="H68" s="148" t="s">
+      <c r="H68" s="142" t="s">
         <v>85</v>
       </c>
-      <c r="I68" s="149"/>
+      <c r="I68" s="143"/>
       <c r="J68" s="84"/>
       <c r="K68" s="113"/>
       <c r="L68" s="4"/>
@@ -5099,12 +5101,12 @@
       <c r="A71" s="30"/>
       <c r="B71" s="125"/>
       <c r="C71" s="126"/>
-      <c r="D71" s="140"/>
-      <c r="E71" s="140"/>
+      <c r="D71" s="230"/>
+      <c r="E71" s="230"/>
       <c r="F71" s="127"/>
       <c r="G71" s="127"/>
-      <c r="H71" s="233"/>
-      <c r="I71" s="233"/>
+      <c r="H71" s="136"/>
+      <c r="I71" s="136"/>
       <c r="J71" s="127"/>
       <c r="K71" s="127"/>
       <c r="L71" s="4"/>
@@ -5130,10 +5132,10 @@
       <c r="G72" s="91" t="s">
         <v>64</v>
       </c>
-      <c r="H72" s="234" t="s">
+      <c r="H72" s="137" t="s">
         <v>89</v>
       </c>
-      <c r="I72" s="234"/>
+      <c r="I72" s="137"/>
       <c r="J72" s="132"/>
       <c r="K72" s="133"/>
       <c r="L72" s="4"/>
@@ -5147,8 +5149,8 @@
       <c r="E73" s="29"/>
       <c r="F73" s="29"/>
       <c r="G73" s="29"/>
-      <c r="H73" s="235"/>
-      <c r="I73" s="235"/>
+      <c r="H73" s="138"/>
+      <c r="I73" s="138"/>
       <c r="J73" s="33"/>
       <c r="K73" s="29"/>
       <c r="L73" s="4"/>
@@ -5162,8 +5164,8 @@
       <c r="E74" s="28"/>
       <c r="F74" s="28"/>
       <c r="G74" s="28"/>
-      <c r="H74" s="231"/>
-      <c r="I74" s="232"/>
+      <c r="H74" s="134"/>
+      <c r="I74" s="135"/>
       <c r="J74" s="32"/>
       <c r="K74" s="35"/>
       <c r="L74" s="4"/>
@@ -5177,8 +5179,8 @@
       <c r="E75" s="28"/>
       <c r="F75" s="28"/>
       <c r="G75" s="28"/>
-      <c r="H75" s="231"/>
-      <c r="I75" s="232"/>
+      <c r="H75" s="134"/>
+      <c r="I75" s="135"/>
       <c r="J75" s="32"/>
       <c r="K75" s="35"/>
       <c r="L75" s="37"/>
@@ -5192,8 +5194,8 @@
       <c r="E76" s="28"/>
       <c r="F76" s="28"/>
       <c r="G76" s="28"/>
-      <c r="H76" s="231"/>
-      <c r="I76" s="232"/>
+      <c r="H76" s="134"/>
+      <c r="I76" s="135"/>
       <c r="J76" s="32"/>
       <c r="K76" s="35"/>
       <c r="L76" s="37"/>
@@ -5207,8 +5209,8 @@
       <c r="E77" s="28"/>
       <c r="F77" s="28"/>
       <c r="G77" s="28"/>
-      <c r="H77" s="231"/>
-      <c r="I77" s="232"/>
+      <c r="H77" s="134"/>
+      <c r="I77" s="135"/>
       <c r="J77" s="32"/>
       <c r="K77" s="35"/>
       <c r="L77" s="4"/>
@@ -5309,25 +5311,61 @@
     </row>
   </sheetData>
   <mergeCells count="90">
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="H77:I77"/>
-    <mergeCell ref="H71:I71"/>
-    <mergeCell ref="H72:I72"/>
-    <mergeCell ref="H73:I73"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="H75:I75"/>
-    <mergeCell ref="C52:F52"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="H56:I56"/>
-    <mergeCell ref="H55:I55"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="H65:I65"/>
+    <mergeCell ref="H66:I66"/>
+    <mergeCell ref="H68:I68"/>
+    <mergeCell ref="C42:G42"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="C48:G48"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="F3:G13"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="J9:K9"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="J10:K10"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="J12:K12"/>
+    <mergeCell ref="C13:E13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="F14:G15"/>
+    <mergeCell ref="H14:I15"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="H16:I16"/>
     <mergeCell ref="C17:I17"/>
     <mergeCell ref="H21:I21"/>
     <mergeCell ref="H22:I22"/>
@@ -5344,61 +5382,25 @@
     <mergeCell ref="H37:I37"/>
     <mergeCell ref="H38:I38"/>
     <mergeCell ref="H40:I40"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="F14:G15"/>
-    <mergeCell ref="H14:I15"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="K15:K16"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="J12:K12"/>
-    <mergeCell ref="C13:E13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="C10:E10"/>
-    <mergeCell ref="J10:K10"/>
-    <mergeCell ref="C11:E11"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="C9:E9"/>
-    <mergeCell ref="J9:K9"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="F3:G13"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="C42:G42"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="C48:G48"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="D71:E71"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="H65:I65"/>
-    <mergeCell ref="H66:I66"/>
-    <mergeCell ref="H68:I68"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="C52:F52"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="H77:I77"/>
+    <mergeCell ref="H71:I71"/>
+    <mergeCell ref="H72:I72"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="H75:I75"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
